--- a/ig/DM_FINESS_New/ValueSet-jdv-mesure-lentille-delivree-cisis.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-jdv-mesure-lentille-delivree-cisis.xlsx
@@ -38,7 +38,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20250606103857</t>
+    <t>20250611134351</t>
   </si>
   <si>
     <t>Name</t>
@@ -68,7 +68,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-06T10:38:57+01:00</t>
+    <t>2025-06-11T13:43:51+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-jdv-mesure-lentille-delivree-cisis.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-jdv-mesure-lentille-delivree-cisis.xlsx
@@ -38,7 +38,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20250611134351</t>
+    <t>20250616134739</t>
   </si>
   <si>
     <t>Name</t>
@@ -68,7 +68,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-11T13:43:51+01:00</t>
+    <t>2025-06-16T13:47:39+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-jdv-mesure-lentille-delivree-cisis.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-jdv-mesure-lentille-delivree-cisis.xlsx
@@ -38,7 +38,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20250616134739</t>
+    <t>20250624152059</t>
   </si>
   <si>
     <t>Name</t>
@@ -68,7 +68,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-16T13:47:39+01:00</t>
+    <t>2025-06-24T15:20:59+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-jdv-mesure-lentille-delivree-cisis.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-jdv-mesure-lentille-delivree-cisis.xlsx
@@ -38,7 +38,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20250624152059</t>
+    <t>20251216141838</t>
   </si>
   <si>
     <t>Name</t>
@@ -68,7 +68,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-24T15:20:59+01:00</t>
+    <t>2025-12-16T14:18:38+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -101,19 +101,13 @@
     <t>Renouvellement</t>
   </si>
   <si>
-    <t>C43383</t>
-  </si>
-  <si>
-    <t>modèle</t>
-  </si>
-  <si>
     <t/>
   </si>
   <si>
     <t>System URI</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/terminologie-ncit</t>
+    <t>http://ncicb.nci.nih.gov/xml/owl/EVS/Thesaurus.owl</t>
   </si>
   <si>
     <t>MED-1181</t>
@@ -177,6 +171,12 @@
   </si>
   <si>
     <t>https://smt.esante.gouv.fr/fhir/CodeSystem/terminologie-cisis</t>
+  </si>
+  <si>
+    <t>67716-1</t>
+  </si>
+  <si>
+    <t>modèle du dispositif</t>
   </si>
   <si>
     <t>95325-7</t>
@@ -453,7 +453,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -481,23 +481,15 @@
         <v>28</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B4" t="s" s="2">
         <v>30</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -524,98 +516,98 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -625,7 +617,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -642,41 +634,49 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>30</v>
+        <v>58</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>30</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B6" t="s" s="2">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>29</v>
+      </c>
+      <c r="B7" t="s" s="2">
         <v>60</v>
       </c>
     </row>

--- a/ig/DM_FINESS_New/ValueSet-jdv-mesure-lentille-delivree-cisis.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-jdv-mesure-lentille-delivree-cisis.xlsx
@@ -38,7 +38,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20251216141838</t>
+    <t>20260220142103</t>
   </si>
   <si>
     <t>Name</t>
@@ -68,7 +68,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-16T14:18:38+01:00</t>
+    <t>2026-02-20T14:21:03+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -95,10 +95,64 @@
     <t>Concept</t>
   </si>
   <si>
-    <t>C53610</t>
-  </si>
-  <si>
-    <t>Renouvellement</t>
+    <t>MED-1181</t>
+  </si>
+  <si>
+    <t>Date de délivrance</t>
+  </si>
+  <si>
+    <t>MED-1183</t>
+  </si>
+  <si>
+    <t>Produit d'entretien</t>
+  </si>
+  <si>
+    <t>MED-1180</t>
+  </si>
+  <si>
+    <t>Type de lentille</t>
+  </si>
+  <si>
+    <t>GEN-292</t>
+  </si>
+  <si>
+    <t>Commentaire</t>
+  </si>
+  <si>
+    <t>MED-1089</t>
+  </si>
+  <si>
+    <t>Diamètre lentille – lentille délivrée</t>
+  </si>
+  <si>
+    <t>MED-1090</t>
+  </si>
+  <si>
+    <t>Rayon 1 lentille – lentille délivrée</t>
+  </si>
+  <si>
+    <t>MED-1091</t>
+  </si>
+  <si>
+    <t>Rayon 2 lentille – lentille délivrée</t>
+  </si>
+  <si>
+    <t>GEN-092.08.04</t>
+  </si>
+  <si>
+    <t>Autre(s) paramètre(s)</t>
+  </si>
+  <si>
+    <t>MED-1092</t>
+  </si>
+  <si>
+    <t>Puissance de la sphère – lentille délivrée</t>
+  </si>
+  <si>
+    <t>MED-1093</t>
+  </si>
+  <si>
+    <t>Puissance du cylindre – lentille délivrée</t>
   </si>
   <si>
     <t/>
@@ -107,76 +161,13 @@
     <t>System URI</t>
   </si>
   <si>
-    <t>http://ncicb.nci.nih.gov/xml/owl/EVS/Thesaurus.owl</t>
-  </si>
-  <si>
-    <t>MED-1181</t>
-  </si>
-  <si>
-    <t>Date de délivrance</t>
-  </si>
-  <si>
-    <t>MED-1183</t>
-  </si>
-  <si>
-    <t>Produit d'entretien</t>
-  </si>
-  <si>
-    <t>MED-1180</t>
-  </si>
-  <si>
-    <t>Type de lentille</t>
-  </si>
-  <si>
-    <t>GEN-292</t>
-  </si>
-  <si>
-    <t>Commentaire</t>
-  </si>
-  <si>
-    <t>MED-1089</t>
-  </si>
-  <si>
-    <t>Diamètre lentille – lentille délivrée</t>
-  </si>
-  <si>
-    <t>MED-1090</t>
-  </si>
-  <si>
-    <t>Rayon 1 lentille – lentille délivrée</t>
-  </si>
-  <si>
-    <t>MED-1091</t>
-  </si>
-  <si>
-    <t>Rayon 2 lentille – lentille délivrée</t>
-  </si>
-  <si>
-    <t>GEN-092.08.04</t>
-  </si>
-  <si>
-    <t>Autre(s) paramètre(s)</t>
-  </si>
-  <si>
-    <t>MED-1092</t>
-  </si>
-  <si>
-    <t>Puissance de la sphère – lentille délivrée</t>
-  </si>
-  <si>
-    <t>MED-1093</t>
-  </si>
-  <si>
-    <t>Puissance du cylindre – lentille délivrée</t>
-  </si>
-  <si>
     <t>https://smt.esante.gouv.fr/fhir/CodeSystem/terminologie-cisis</t>
   </si>
   <si>
     <t>67716-1</t>
   </si>
   <si>
-    <t>modèle du dispositif</t>
+    <t>Modèle du dispositif</t>
   </si>
   <si>
     <t>95325-7</t>
@@ -198,6 +189,15 @@
   </si>
   <si>
     <t>http://loinc.org</t>
+  </si>
+  <si>
+    <t>103742009</t>
+  </si>
+  <si>
+    <t>renouvellement d'ordonnance</t>
+  </si>
+  <si>
+    <t>http://snomed.info/sct</t>
   </si>
 </sst>
 </file>
@@ -453,52 +453,6 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <cols>
-    <col min="1" max="1" width="30.703125" customWidth="true"/>
-    <col min="2" max="2" width="50.703125" customWidth="true"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="1">
-        <v>25</v>
-      </c>
-      <c r="B1" t="s" s="1">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>26</v>
-      </c>
-      <c r="B2" t="s" s="2">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>28</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>29</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>30</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
@@ -516,98 +470,98 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>32</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>34</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>36</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>38</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>42</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>44</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>46</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>28</v>
+        <v>46</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -615,7 +569,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
@@ -634,49 +588,95 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>28</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="B7" t="s" s="2">
+        <v>57</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>25</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B4" t="s" s="2">
         <v>60</v>
       </c>
     </row>

--- a/ig/DM_FINESS_New/ValueSet-jdv-mesure-lentille-delivree-cisis.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-jdv-mesure-lentille-delivree-cisis.xlsx
@@ -38,7 +38,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260220142103</t>
+    <t>20260311144902</t>
   </si>
   <si>
     <t>Name</t>
@@ -68,7 +68,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-20T14:21:03+01:00</t>
+    <t>2026-03-11T14:49:02+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-jdv-mesure-lentille-delivree-cisis.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-jdv-mesure-lentille-delivree-cisis.xlsx
@@ -38,7 +38,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260311144902</t>
+    <t>20260420150249</t>
   </si>
   <si>
     <t>Name</t>
@@ -68,7 +68,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-11T14:49:02+01:00</t>
+    <t>2026-04-20T15:02:49+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-jdv-mesure-lentille-delivree-cisis.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-jdv-mesure-lentille-delivree-cisis.xlsx
@@ -38,7 +38,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260420150249</t>
+    <t>20260619134041</t>
   </si>
   <si>
     <t>Name</t>
@@ -68,7 +68,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T15:02:49+01:00</t>
+    <t>2026-06-19T13:40:41+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
